--- a/SGC-CKN/Excel/3f3d2d48-cc4d-4af7-8c1e-488fce9246f7_Thi_công_cọc_khoan_nhồi_P1-54_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/3f3d2d48-cc4d-4af7-8c1e-488fce9246f7_Thi_công_cọc_khoan_nhồi_P1-54_D800_29-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -180,6 +180,9 @@
   <si>
     <t xml:space="preserve">20:45
 29/03/2026</t>
+  </si>
+  <si>
+    <t>CĐ CS -35,81</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1151,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-4.4</v>
+        <v>-1.4</v>
       </c>
       <c r="H11" s="5">
         <v>0.15</v>
       </c>
       <c r="I11" s="5">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="8">
-        <v>29.33</v>
+        <v>9.33</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1183,19 +1186,19 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-4.4</v>
+        <v>-1.4</v>
       </c>
       <c r="G12" s="9">
-        <v>-7.7</v>
+        <v>-4.3</v>
       </c>
       <c r="H12" s="9">
         <v>0.35</v>
       </c>
       <c r="I12" s="9">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J12" s="8">
-        <v>9.43</v>
+        <v>8.29</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1218,19 +1221,19 @@
         <v>36</v>
       </c>
       <c r="F13" s="12">
+        <v>-4.3</v>
+      </c>
+      <c r="G13" s="12">
         <v>-7.7</v>
-      </c>
-      <c r="G13" s="12">
-        <v>-16.5</v>
       </c>
       <c r="H13" s="12">
         <v>0.5</v>
       </c>
       <c r="I13" s="12">
-        <v>8.8</v>
+        <v>3.4</v>
       </c>
       <c r="J13" s="8">
-        <v>17.6</v>
+        <v>6.8</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1253,19 +1256,19 @@
         <v>39</v>
       </c>
       <c r="F14" s="15">
+        <v>-7.7</v>
+      </c>
+      <c r="G14" s="15">
         <v>-16.5</v>
-      </c>
-      <c r="G14" s="15">
-        <v>-21.8</v>
       </c>
       <c r="H14" s="15">
         <v>0.67</v>
       </c>
       <c r="I14" s="15">
-        <v>5.3</v>
+        <v>8.8</v>
       </c>
       <c r="J14" s="8">
-        <v>7.95</v>
+        <v>13.2</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1288,19 +1291,19 @@
         <v>42</v>
       </c>
       <c r="F15" s="18">
+        <v>-16.5</v>
+      </c>
+      <c r="G15" s="18">
         <v>-21.8</v>
-      </c>
-      <c r="G15" s="18">
-        <v>-25.7</v>
       </c>
       <c r="H15" s="18">
         <v>2.17</v>
       </c>
       <c r="I15" s="18">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="J15" s="21">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1323,19 +1326,19 @@
         <v>45</v>
       </c>
       <c r="F16" s="22">
+        <v>-21.8</v>
+      </c>
+      <c r="G16" s="22">
         <v>-25.7</v>
-      </c>
-      <c r="G16" s="22">
-        <v>-39.5</v>
       </c>
       <c r="H16" s="22">
         <v>2.67</v>
       </c>
       <c r="I16" s="22">
-        <v>13.8</v>
-      </c>
-      <c r="J16" s="8">
-        <v>5.18</v>
+        <v>3.9</v>
+      </c>
+      <c r="J16" s="21">
+        <v>1.46</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1358,19 +1361,19 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
+        <v>-25.7</v>
+      </c>
+      <c r="G17" s="25">
         <v>-39.5</v>
-      </c>
-      <c r="G17" s="25">
-        <v>-44.2</v>
       </c>
       <c r="H17" s="25">
         <v>1.67</v>
       </c>
       <c r="I17" s="25">
-        <v>4.7</v>
-      </c>
-      <c r="J17" s="21">
-        <v>2.82</v>
+        <v>13.8</v>
+      </c>
+      <c r="J17" s="8">
+        <v>8.28</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
@@ -1393,7 +1396,7 @@
         <v>52</v>
       </c>
       <c r="F18" s="28">
-        <v>-44.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G18" s="28">
         <v>-44.2</v>
@@ -1402,18 +1405,18 @@
         <v>3.08</v>
       </c>
       <c r="I18" s="28">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J18" s="21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1519,31 +1522,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1563,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-4.4</v>
+        <v>-1.4</v>
       </c>
       <c r="G2" s="5">
         <v>0.15</v>
       </c>
       <c r="H2" s="5">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="I2" s="8">
-        <v>29.33</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1589,19 +1592,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-4.4</v>
+        <v>-1.4</v>
       </c>
       <c r="F3" s="9">
-        <v>-7.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G3" s="9">
         <v>0.35</v>
       </c>
       <c r="H3" s="9">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="I3" s="8">
-        <v>9.43</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1618,19 +1621,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
+        <v>-4.3</v>
+      </c>
+      <c r="F4" s="12">
         <v>-7.7</v>
-      </c>
-      <c r="F4" s="12">
-        <v>-16.5</v>
       </c>
       <c r="G4" s="12">
         <v>0.5</v>
       </c>
       <c r="H4" s="12">
-        <v>8.8</v>
+        <v>3.4</v>
       </c>
       <c r="I4" s="8">
-        <v>17.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1647,19 +1650,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
+        <v>-7.7</v>
+      </c>
+      <c r="F5" s="15">
         <v>-16.5</v>
-      </c>
-      <c r="F5" s="15">
-        <v>-21.8</v>
       </c>
       <c r="G5" s="15">
         <v>0.67</v>
       </c>
       <c r="H5" s="15">
-        <v>5.3</v>
+        <v>8.8</v>
       </c>
       <c r="I5" s="8">
-        <v>7.95</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1676,19 +1679,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="18">
+        <v>-16.5</v>
+      </c>
+      <c r="F6" s="18">
         <v>-21.8</v>
-      </c>
-      <c r="F6" s="18">
-        <v>-25.7</v>
       </c>
       <c r="G6" s="18">
         <v>2.17</v>
       </c>
       <c r="H6" s="18">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="21">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1705,19 +1708,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
+        <v>-21.8</v>
+      </c>
+      <c r="F7" s="22">
         <v>-25.7</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-39.5</v>
       </c>
       <c r="G7" s="22">
         <v>2.67</v>
       </c>
       <c r="H7" s="22">
-        <v>13.8</v>
-      </c>
-      <c r="I7" s="8">
-        <v>5.18</v>
+        <v>3.9</v>
+      </c>
+      <c r="I7" s="21">
+        <v>1.46</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1734,19 +1737,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
+        <v>-25.7</v>
+      </c>
+      <c r="F8" s="25">
         <v>-39.5</v>
-      </c>
-      <c r="F8" s="25">
-        <v>-44.2</v>
       </c>
       <c r="G8" s="25">
         <v>1.67</v>
       </c>
       <c r="H8" s="25">
-        <v>4.7</v>
-      </c>
-      <c r="I8" s="21">
-        <v>2.82</v>
+        <v>13.8</v>
+      </c>
+      <c r="I8" s="8">
+        <v>8.28</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-44.2</v>
+        <v>-39.5</v>
       </c>
       <c r="F9" s="28">
         <v>-44.2</v>
@@ -1772,15 +1775,15 @@
         <v>3.08</v>
       </c>
       <c r="H9" s="28">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I9" s="21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
